--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Collegetown_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +454,14 @@
           <t>Capers</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>65.24</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>65.24</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>65.23999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Monin - Vanilla</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>35.21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35.21</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.21</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Oat Milk</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>80.45</t>
-        </is>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80.45</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Pastrami (Sliced)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>66.45</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>132.90</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="E5" t="n">
+        <v>132.9</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Corned Beef (Sliced)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>66.26</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66.26</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>66.26000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Chicken Breast - Retail (cooked)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>59.22</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>177.66</t>
-        </is>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>177.66</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Avocado - Hand Scooped</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>57.63</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>172.89</t>
-        </is>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E8" t="n">
+        <v>172.89</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Cream Cheese</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>62.00</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>124.00</t>
-        </is>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>62</v>
+      </c>
+      <c r="E9" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>English Muffin</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>55.96</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="E10" t="n">
+        <v>55.96</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Almond Milk</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>35.74</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>214.44</t>
-        </is>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="E11" t="n">
+        <v>214.44</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Fresh Mozz (Sliced)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>50.19</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>100.38</t>
-        </is>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100.38</v>
       </c>
     </row>
     <row r="13">
@@ -751,20 +685,14 @@
           <t>Swiss (Sliced)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>56.88</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>56.88</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56.88</v>
       </c>
     </row>
     <row r="14">
@@ -778,20 +706,14 @@
           <t>Pepper Jack (Sliced)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>53.03</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>159.09</t>
-        </is>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="E14" t="n">
+        <v>159.09</v>
       </c>
     </row>
     <row r="15">
@@ -805,20 +727,14 @@
           <t>Edamame - FRZ Shelled</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>48</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -832,20 +748,14 @@
           <t>Mousse Cup - Chocolate</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>93.75</t>
-        </is>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>93.75</v>
       </c>
     </row>
     <row r="17">
@@ -859,20 +769,14 @@
           <t>Roma - Tiramisu Plastic Cup</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>101.43</t>
-        </is>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="E17" t="n">
+        <v>101.43</v>
       </c>
     </row>
     <row r="18">
@@ -886,20 +790,14 @@
           <t>Poland Spring - Sport Top</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>33.27</t>
-        </is>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="E18" t="n">
+        <v>33.27</v>
       </c>
     </row>
     <row r="19">
@@ -913,20 +811,14 @@
           <t>Spindrift - Lime</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="E19" t="n">
+        <v>24.71</v>
       </c>
     </row>
     <row r="20">
@@ -940,20 +832,14 @@
           <t>Spindrift - Orange Mango</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>24.96</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>24.96</t>
-        </is>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24.96</v>
       </c>
     </row>
     <row r="21">
@@ -967,20 +853,14 @@
           <t>Spindrift - Lemon</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>24.83</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>24.83</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="E21" t="n">
+        <v>24.83</v>
       </c>
     </row>
     <row r="22">
@@ -994,20 +874,14 @@
           <t>Spindrift - Half &amp; Half</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>23.75</v>
       </c>
     </row>
     <row r="23">
@@ -1021,20 +895,56 @@
           <t>Sparkling Ice - Orange Mango</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="E23" t="n">
+        <v>24.64</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TN330</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Natalie's - Honey Tangerine</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TN380</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Natalie's - Strawberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10.15</v>
       </c>
     </row>
   </sheetData>
